--- a/database/NFs.xlsx
+++ b/database/NFs.xlsx
@@ -34,52 +34,16 @@
     <t>EX</t>
   </si>
   <si>
-    <t>DTR0000015396</t>
-  </si>
-  <si>
     <t>MT</t>
-  </si>
-  <si>
-    <t>DTR0009907851</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
-    <t>AA00002273914</t>
-  </si>
-  <si>
     <t>CN</t>
   </si>
   <si>
-    <t>DTR0009907842</t>
-  </si>
-  <si>
-    <t>DTR0000471764</t>
-  </si>
-  <si>
-    <t>DTR0009907741</t>
-  </si>
-  <si>
-    <t>DTR0009907740</t>
-  </si>
-  <si>
-    <t>DTR0009907739</t>
-  </si>
-  <si>
     <t>RO</t>
-  </si>
-  <si>
-    <t>DTR0009907841</t>
-  </si>
-  <si>
-    <t>DTR0009907822</t>
-  </si>
-  <si>
-    <t>DTR0009907737</t>
-  </si>
-  <si>
-    <t>DTR0000388840</t>
   </si>
   <si>
     <t>project_id</t>
@@ -110,6 +74,42 @@
   </si>
   <si>
     <t>company_id</t>
+  </si>
+  <si>
+    <t>0015396</t>
+  </si>
+  <si>
+    <t>2273914</t>
+  </si>
+  <si>
+    <t>9907842</t>
+  </si>
+  <si>
+    <t>0471764</t>
+  </si>
+  <si>
+    <t>9907741</t>
+  </si>
+  <si>
+    <t>9907740</t>
+  </si>
+  <si>
+    <t>9907739</t>
+  </si>
+  <si>
+    <t>9907841</t>
+  </si>
+  <si>
+    <t>9907851</t>
+  </si>
+  <si>
+    <t>9907822</t>
+  </si>
+  <si>
+    <t>9907737</t>
+  </si>
+  <si>
+    <t>0388840</t>
   </si>
 </sst>
 </file>
@@ -464,34 +464,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="J1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -505,7 +505,7 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E2">
         <v>40</v>
@@ -515,7 +515,7 @@
         <v>40</v>
       </c>
       <c r="G2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>77.08</v>
@@ -538,7 +538,7 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -571,7 +571,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E4">
         <v>6</v>
@@ -604,7 +604,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E5">
         <v>6</v>
@@ -620,7 +620,7 @@
         <v>35316.514300000003</v>
       </c>
       <c r="I5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>5</v>
@@ -637,7 +637,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -653,7 +653,7 @@
         <v>39772.757899999997</v>
       </c>
       <c r="I6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -670,7 +670,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -686,7 +686,7 @@
         <v>39416.380899999996</v>
       </c>
       <c r="I7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -703,7 +703,7 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E8">
         <v>6</v>
@@ -719,7 +719,7 @@
         <v>34096.050799999997</v>
       </c>
       <c r="I8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -736,7 +736,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E9">
         <v>6</v>
@@ -752,7 +752,7 @@
         <v>41184.7166</v>
       </c>
       <c r="I9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -769,7 +769,7 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E10">
         <v>80</v>
@@ -802,7 +802,7 @@
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E11">
         <v>9887</v>
@@ -835,7 +835,7 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E12">
         <v>2000</v>
@@ -868,7 +868,7 @@
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E13">
         <v>2000</v>
@@ -901,7 +901,7 @@
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E14">
         <v>43215</v>
@@ -934,7 +934,7 @@
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E15">
         <v>4426</v>
@@ -967,7 +967,7 @@
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E16">
         <v>4970</v>
@@ -1000,7 +1000,7 @@
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E17">
         <v>6</v>
@@ -1016,7 +1016,7 @@
         <v>52452.805099999998</v>
       </c>
       <c r="I17" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>5</v>
@@ -1033,7 +1033,7 @@
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E18">
         <v>1400</v>
@@ -1066,7 +1066,7 @@
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E19">
         <v>394</v>
@@ -1099,7 +1099,7 @@
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E20">
         <v>432</v>
@@ -1115,7 +1115,7 @@
         <v>0.2223</v>
       </c>
       <c r="I20" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>5</v>
@@ -1132,7 +1132,7 @@
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E21">
         <v>624</v>
@@ -1148,7 +1148,7 @@
         <v>0.19889999999999999</v>
       </c>
       <c r="I21" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>5</v>
@@ -1165,7 +1165,7 @@
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E22">
         <v>144</v>
@@ -1181,7 +1181,7 @@
         <v>0.26910000000000001</v>
       </c>
       <c r="I22" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>5</v>
@@ -1198,7 +1198,7 @@
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E23">
         <v>144</v>
@@ -1214,7 +1214,7 @@
         <v>0.60840000000000005</v>
       </c>
       <c r="I23" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>5</v>
@@ -1231,7 +1231,7 @@
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E24">
         <v>366</v>
@@ -1264,7 +1264,7 @@
         <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E25">
         <v>8006</v>
@@ -1297,7 +1297,7 @@
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E26">
         <v>6369</v>
@@ -1330,7 +1330,7 @@
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E27">
         <v>3410</v>
@@ -1363,7 +1363,7 @@
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E28">
         <v>6000</v>
@@ -1396,7 +1396,7 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E29">
         <v>3500</v>
@@ -1429,7 +1429,7 @@
         <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E30">
         <v>178</v>
@@ -1462,7 +1462,7 @@
         <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E31">
         <v>14768</v>
@@ -1495,7 +1495,7 @@
         <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E32">
         <v>5895</v>
@@ -1528,7 +1528,7 @@
         <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E33">
         <v>200</v>
@@ -1561,7 +1561,7 @@
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E34">
         <v>1631</v>
@@ -1594,7 +1594,7 @@
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E35">
         <v>3000</v>
@@ -1627,7 +1627,7 @@
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E36">
         <v>105</v>
@@ -1660,7 +1660,7 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E37">
         <v>3114</v>
@@ -1693,7 +1693,7 @@
         <v>8</v>
       </c>
       <c r="D38" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E38">
         <v>12364</v>
@@ -1726,7 +1726,7 @@
         <v>8</v>
       </c>
       <c r="D39" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E39">
         <v>6378</v>
@@ -1759,7 +1759,7 @@
         <v>8</v>
       </c>
       <c r="D40" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E40">
         <v>1490</v>
@@ -1792,7 +1792,7 @@
         <v>8</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E41">
         <v>10</v>
@@ -1825,7 +1825,7 @@
         <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E42">
         <v>18410</v>
@@ -1858,7 +1858,7 @@
         <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E43">
         <v>2010</v>
@@ -1891,7 +1891,7 @@
         <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E44">
         <v>4</v>
@@ -1924,7 +1924,7 @@
         <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E45">
         <v>4</v>
@@ -1957,7 +1957,7 @@
         <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E46">
         <v>10206</v>
@@ -1990,7 +1990,7 @@
         <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E47">
         <v>5659</v>
@@ -2023,7 +2023,7 @@
         <v>8</v>
       </c>
       <c r="D48" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E48">
         <v>50282</v>
@@ -2056,7 +2056,7 @@
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E49">
         <v>16797</v>
@@ -2089,7 +2089,7 @@
         <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E50">
         <v>528</v>
@@ -2122,7 +2122,7 @@
         <v>8</v>
       </c>
       <c r="D51" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E51">
         <v>4</v>
@@ -2155,7 +2155,7 @@
         <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E52">
         <v>150</v>
@@ -2165,7 +2165,7 @@
         <v>150</v>
       </c>
       <c r="G52" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H52">
         <v>63.99</v>
@@ -2188,7 +2188,7 @@
         <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E53">
         <v>2613</v>
@@ -2221,7 +2221,7 @@
         <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E54">
         <v>178</v>
@@ -2254,7 +2254,7 @@
         <v>8</v>
       </c>
       <c r="D55" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E55">
         <v>6542</v>
@@ -2287,7 +2287,7 @@
         <v>8</v>
       </c>
       <c r="D56" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E56">
         <v>5294</v>
@@ -2320,7 +2320,7 @@
         <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E57">
         <v>1000</v>
@@ -2353,7 +2353,7 @@
         <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E58">
         <v>3</v>
@@ -2369,7 +2369,7 @@
         <v>41146.6636</v>
       </c>
       <c r="I58" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J58">
         <v>5</v>
@@ -2386,7 +2386,7 @@
         <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E59">
         <v>3</v>
@@ -2402,7 +2402,7 @@
         <v>40159.411999999997</v>
       </c>
       <c r="I59" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J59">
         <v>5</v>
@@ -2419,7 +2419,7 @@
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E60">
         <v>8680</v>
@@ -2452,7 +2452,7 @@
         <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E61">
         <v>110</v>
@@ -2485,7 +2485,7 @@
         <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E62">
         <v>200</v>
@@ -2495,7 +2495,7 @@
         <v>200</v>
       </c>
       <c r="G62" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H62">
         <v>63.99</v>
@@ -2518,7 +2518,7 @@
         <v>8</v>
       </c>
       <c r="D63" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E63">
         <v>3785</v>
@@ -2551,7 +2551,7 @@
         <v>8</v>
       </c>
       <c r="D64" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E64">
         <v>4584</v>
@@ -2584,7 +2584,7 @@
         <v>8</v>
       </c>
       <c r="D65" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E65">
         <v>4500</v>
@@ -2617,7 +2617,7 @@
         <v>8</v>
       </c>
       <c r="D66" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E66">
         <v>37</v>
@@ -2627,7 +2627,7 @@
         <v>37</v>
       </c>
       <c r="G66" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H66">
         <v>63.99</v>
@@ -2650,7 +2650,7 @@
         <v>8</v>
       </c>
       <c r="D67" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E67">
         <v>21</v>
@@ -2660,7 +2660,7 @@
         <v>21</v>
       </c>
       <c r="G67" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H67">
         <v>52.471800000000002</v>
@@ -2683,7 +2683,7 @@
         <v>8</v>
       </c>
       <c r="D68" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E68">
         <v>21549</v>
@@ -2716,7 +2716,7 @@
         <v>8</v>
       </c>
       <c r="D69" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E69">
         <v>770</v>
@@ -2749,7 +2749,7 @@
         <v>8</v>
       </c>
       <c r="D70" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E70">
         <v>11925</v>
@@ -2782,7 +2782,7 @@
         <v>8</v>
       </c>
       <c r="D71" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E71">
         <v>15808</v>
@@ -2815,7 +2815,7 @@
         <v>8</v>
       </c>
       <c r="D72" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E72">
         <v>664</v>
@@ -2848,7 +2848,7 @@
         <v>8</v>
       </c>
       <c r="D73" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E73">
         <v>900</v>
@@ -2881,7 +2881,7 @@
         <v>8</v>
       </c>
       <c r="D74" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E74">
         <v>2800</v>
@@ -2914,7 +2914,7 @@
         <v>8</v>
       </c>
       <c r="D75" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E75">
         <v>28324</v>
@@ -2947,7 +2947,7 @@
         <v>8</v>
       </c>
       <c r="D76" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E76">
         <v>14750</v>
@@ -2980,7 +2980,7 @@
         <v>8</v>
       </c>
       <c r="D77" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E77">
         <v>16376</v>
@@ -3013,7 +3013,7 @@
         <v>8</v>
       </c>
       <c r="D78" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E78">
         <v>1516</v>
@@ -3046,7 +3046,7 @@
         <v>8</v>
       </c>
       <c r="D79" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E79">
         <v>16051</v>
@@ -3079,7 +3079,7 @@
         <v>8</v>
       </c>
       <c r="D80" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E80">
         <v>7000</v>
@@ -3112,7 +3112,7 @@
         <v>8</v>
       </c>
       <c r="D81" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E81">
         <v>8624</v>
@@ -3145,7 +3145,7 @@
         <v>8</v>
       </c>
       <c r="D82" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E82">
         <v>8584</v>
@@ -3178,7 +3178,7 @@
         <v>8</v>
       </c>
       <c r="D83" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E83">
         <v>3120</v>
@@ -3211,7 +3211,7 @@
         <v>8</v>
       </c>
       <c r="D84" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E84">
         <v>4000</v>
@@ -3244,7 +3244,7 @@
         <v>8</v>
       </c>
       <c r="D85" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E85">
         <v>30000</v>
@@ -3277,7 +3277,7 @@
         <v>8</v>
       </c>
       <c r="D86" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E86">
         <v>2716</v>
@@ -3310,7 +3310,7 @@
         <v>8</v>
       </c>
       <c r="D87" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E87">
         <v>16200</v>
@@ -3343,7 +3343,7 @@
         <v>8</v>
       </c>
       <c r="D88" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E88">
         <v>700</v>
@@ -3376,7 +3376,7 @@
         <v>8</v>
       </c>
       <c r="D89" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E89">
         <v>2050</v>
@@ -3409,7 +3409,7 @@
         <v>8</v>
       </c>
       <c r="D90" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E90">
         <v>6302</v>
@@ -3442,7 +3442,7 @@
         <v>8</v>
       </c>
       <c r="D91" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E91">
         <v>4000</v>
@@ -3475,7 +3475,7 @@
         <v>8</v>
       </c>
       <c r="D92" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E92">
         <v>1066</v>
@@ -3508,7 +3508,7 @@
         <v>8</v>
       </c>
       <c r="D93" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E93">
         <v>2103</v>
@@ -3541,7 +3541,7 @@
         <v>8</v>
       </c>
       <c r="D94" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E94">
         <v>485</v>
@@ -3574,7 +3574,7 @@
         <v>8</v>
       </c>
       <c r="D95" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E95">
         <v>700</v>
@@ -3607,7 +3607,7 @@
         <v>8</v>
       </c>
       <c r="D96" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E96">
         <v>1230</v>
